--- a/informe_hotel_PUQ.xlsx
+++ b/informe_hotel_PUQ.xlsx
@@ -72,12 +72,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -456,12 +462,12 @@
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="27" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
@@ -485,6 +491,41 @@
           <t>No seleccionado</t>
         </is>
       </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Singles M</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Dobles M</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Singles F</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Dobles F</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Total Singles</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Total Dobles</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -497,6 +538,29 @@
           <t>No seleccionado</t>
         </is>
       </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -509,6 +573,29 @@
           <t>16-11-2024</t>
         </is>
       </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -521,6 +608,29 @@
           <t>16-11-2024</t>
         </is>
       </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -536,4812 +646,4812 @@
     </row>
     <row r="7"/>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Nro</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>First name</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Last name</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Gender</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Nacionalidad</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Hotel Ciudad</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Check in</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>Check out</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>Rooms</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="M8" s="5" t="inlineStr">
         <is>
           <t>Grupo</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>SCHMIDT</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> FRANZISKA</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>f</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Doctor</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>PUQ, Cabo de Hornos</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="K9" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="L9" s="6" t="inlineStr">
         <is>
           <t>single f</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="M9" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>HANSEN-LINDSTROM</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> ULF-PETER MAGNUS</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Finland</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>Captain</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>PUQ, Cabo de Hornos</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="K10" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="L10" s="6" t="inlineStr">
         <is>
           <t>single m</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="M10" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>GULINO</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> SIMONE</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Chief Engineer</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>PUQ, Cabo de Hornos</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="K11" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="L11" s="6" t="inlineStr">
         <is>
           <t>single m</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="M11" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>BORDEI</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> SILVIU DUMITRU</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Romania</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Financial Officer</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>PUQ, Cabo de Hornos</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="K12" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="L12" s="6" t="inlineStr">
         <is>
           <t>single m</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="M12" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> TAMARA</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>HOFER</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>f</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Austria</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Financial Officer</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>PUQ, Cabo de Hornos</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="K13" s="6" t="inlineStr">
         <is>
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="L13" s="6" t="inlineStr">
         <is>
           <t>single f</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="M13" s="6" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> KADEK</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>SETIAWAN</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>Indonesia</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>Chef De Partie</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>PUQ, Art Noveau</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="K14" s="6" t="inlineStr">
         <is>
           <t>2024-11-20</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="L14" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="M14" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>AHMED</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> ALTAF</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Senior Security Guard</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>PUQ, Los Navegantes</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="K15" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="L15" s="6" t="inlineStr">
         <is>
           <t>single m</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="M15" s="6" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>BOCCIA</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> ANTONIO</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>Executive Sous Chef</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>PUQ, Los Navegantes</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J16" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="K16" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="L16" s="6" t="inlineStr">
         <is>
           <t>single m</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="M16" s="6" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>ARLEN</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>RIVERA</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>Hotel Store Manager</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>PUQ, Los Navegantes</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J17" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K17" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L17" s="6" t="inlineStr">
         <is>
           <t>single m</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M17" s="6" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> RYO ADI</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">SAPUTRA </t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>Indonesia</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>Suite Attendant</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>PUQ, Art Noveau</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J18" s="6" t="inlineStr">
         <is>
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="K18" s="6" t="inlineStr">
         <is>
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="L18" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="M18" s="6" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>MASILI</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> ANGELO</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>1st Hotel Engineer</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>PUQ, Carpa Manzano</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J19" s="6" t="inlineStr">
         <is>
           <t>2024-11-13</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K19" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L19" s="6" t="inlineStr">
         <is>
           <t>single m</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M19" s="6" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">KAPOMBE </t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> MIREILLE</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>f</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>Congo</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>Waiter</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>PUQ, Kran Keen</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J20" s="6" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="K20" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="L20" s="6" t="inlineStr">
         <is>
           <t>doble f</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="M20" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>GAY-YA</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> FELICIANA</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>f</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>Desktop Publisher</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>PUQ, Kran Keen</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J21" s="6" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K21" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="L21" s="6" t="inlineStr">
         <is>
           <t>doble f</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="M21" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>GROMIO</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> KIMBERLY PANUGAO</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>f</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>Bar Waiter/Waitress</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>PUQ, TBC</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J22" s="6" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="K22" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="L22" s="6" t="inlineStr">
         <is>
           <t>doble f</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="M22" s="6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>NUNEZ</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> SHELLA GADUGDUG</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>f</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>Junior Nurse</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>PUQ, TBC</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J23" s="6" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="K23" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="L23" s="6" t="inlineStr">
         <is>
           <t>doble f</t>
         </is>
       </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="M23" s="6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>BISHT</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> LALIT</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>Service Assistant</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>PUQ, Kran Keen</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J24" s="6" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="K24" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="L24" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="M24" s="6" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">KALIM </t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> MAZHAR</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>Butler</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>PUQ, Kran Keen</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="J25" s="6" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="K25" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr">
+      <c r="L25" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="M25" s="6" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>SAHA</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> SOUVIK</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>Suite Attendant</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>PUQ, Kran Keen</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="J26" s="6" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="K26" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L26" s="4" t="inlineStr">
+      <c r="L26" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="M26" s="6" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>VELANKOVIL RAJU</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> RENJITH MON</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>Galley Utility</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>PUQ, Kran Keen</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="J27" s="6" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="K27" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L27" s="4" t="inlineStr">
+      <c r="L27" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="M27" s="6" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n">
+      <c r="A28" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>NYARIKI</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> MARTIN</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>Kenya</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>2nd Cook</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>PUQ, Kran Keen</t>
         </is>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="J28" s="6" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
+      <c r="K28" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L28" s="4" t="inlineStr">
+      <c r="L28" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="M28" s="6" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>OWIYO</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> ERICK ODONGO</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>Kenya</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>PUQ, TBC</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="J29" s="6" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="K29" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="L29" s="4" t="inlineStr">
+      <c r="L29" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M29" s="4" t="inlineStr">
+      <c r="M29" s="6" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n">
+      <c r="A30" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>AGUSTIN</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> GARRY</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>2nd Cook</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
         <is>
           <t>PUQ, Kran Keen</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="J30" s="6" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr">
+      <c r="K30" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L30" s="4" t="inlineStr">
+      <c r="L30" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="M30" s="6" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>AREVALO</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> TIMOTEO JR. BARNES</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>Carpenter</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
         <is>
           <t>PUQ, Kran Keen</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="J31" s="6" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr">
+      <c r="K31" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L31" s="4" t="inlineStr">
+      <c r="L31" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M31" s="4" t="inlineStr">
+      <c r="M31" s="6" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n">
+      <c r="A32" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>BARLAAN</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> MARLON</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>Chef De Partie</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
         <is>
           <t>PUQ, Kran Keen</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr">
+      <c r="J32" s="6" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr">
+      <c r="K32" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L32" s="4" t="inlineStr">
+      <c r="L32" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M32" s="4" t="inlineStr">
+      <c r="M32" s="6" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>CASTILLON</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> JOLLY PANTORILLA</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>Able Seaman</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
         <is>
           <t>PUQ, Kran Keen</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="J33" s="6" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="K33" s="4" t="inlineStr">
+      <c r="K33" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L33" s="4" t="inlineStr">
+      <c r="L33" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M33" s="4" t="inlineStr">
+      <c r="M33" s="6" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="n">
+      <c r="A34" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>HULLANA</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> RAYMUND GARRIDO</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>IT/Communications Officer</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
         <is>
           <t>PUQ, Carpa Manzano</t>
         </is>
       </c>
-      <c r="J34" s="4" t="inlineStr">
+      <c r="J34" s="6" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="K34" s="4" t="inlineStr">
+      <c r="K34" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L34" s="4" t="inlineStr">
+      <c r="L34" s="6" t="inlineStr">
         <is>
           <t>single m</t>
         </is>
       </c>
-      <c r="M34" s="4" t="inlineStr">
+      <c r="M34" s="6" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n">
+      <c r="A35" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>LAURENTE</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> REYMARK</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="G35" s="6" t="inlineStr">
         <is>
           <t>Able Seaman</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
         <is>
           <t>PUQ, TBC</t>
         </is>
       </c>
-      <c r="J35" s="4" t="inlineStr">
+      <c r="J35" s="6" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="K35" s="4" t="inlineStr">
+      <c r="K35" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="L35" s="4" t="inlineStr">
+      <c r="L35" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M35" s="4" t="inlineStr">
+      <c r="M35" s="6" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
+      <c r="A36" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>MACAPOBRE</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> HOMBRE</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>Able Seaman</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
         <is>
           <t>PUQ, Kran Keen</t>
         </is>
       </c>
-      <c r="J36" s="4" t="inlineStr">
+      <c r="J36" s="6" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="K36" s="4" t="inlineStr">
+      <c r="K36" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L36" s="4" t="inlineStr">
+      <c r="L36" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M36" s="4" t="inlineStr">
+      <c r="M36" s="6" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n">
+      <c r="A37" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>MAGDADARO</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> RAFFY</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G37" s="6" t="inlineStr">
         <is>
           <t>Oiler</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>PUQ, TBC</t>
         </is>
       </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="J37" s="6" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="K37" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="L37" s="4" t="inlineStr">
+      <c r="L37" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M37" s="4" t="inlineStr">
+      <c r="M37" s="6" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n">
+      <c r="A38" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>NAVARRETE</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> RUEL</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="G38" s="6" t="inlineStr">
         <is>
           <t>Fitter</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
         <is>
           <t>PUQ, Kran Keen</t>
         </is>
       </c>
-      <c r="J38" s="4" t="inlineStr">
+      <c r="J38" s="6" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="K38" s="4" t="inlineStr">
+      <c r="K38" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L38" s="4" t="inlineStr">
+      <c r="L38" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M38" s="4" t="inlineStr">
+      <c r="M38" s="6" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>ORFANO</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> NICANOR PANERGO</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>Provision Man</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I39" s="4" t="inlineStr">
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
         <is>
           <t>PUQ, TBC</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr">
+      <c r="J39" s="6" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="K39" s="4" t="inlineStr">
+      <c r="K39" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="L39" s="4" t="inlineStr">
+      <c r="L39" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M39" s="4" t="inlineStr">
+      <c r="M39" s="6" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n">
+      <c r="A40" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>SAMSON</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> PAUL ALDRIN </t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>Galley Utility</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
         <is>
           <t>PUQ, Kran Keen</t>
         </is>
       </c>
-      <c r="J40" s="4" t="inlineStr">
+      <c r="J40" s="6" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="K40" s="4" t="inlineStr">
+      <c r="K40" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L40" s="4" t="inlineStr">
+      <c r="L40" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M40" s="4" t="inlineStr">
+      <c r="M40" s="6" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
+      <c r="A41" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>VALENCIA</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> ALFIE TRISTAN</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>Pastry Chef</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
         <is>
           <t>PUQ, TBC</t>
         </is>
       </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="J41" s="6" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="K41" s="4" t="inlineStr">
+      <c r="K41" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L41" s="4" t="inlineStr">
+      <c r="L41" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M41" s="4" t="inlineStr">
+      <c r="M41" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n">
+      <c r="A42" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>VILLA</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> ORLANDO</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>Butler</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I42" s="4" t="inlineStr">
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
         <is>
           <t>PUQ, Kran Keen</t>
         </is>
       </c>
-      <c r="J42" s="4" t="inlineStr">
+      <c r="J42" s="6" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="K42" s="4" t="inlineStr">
+      <c r="K42" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L42" s="4" t="inlineStr">
+      <c r="L42" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M42" s="4" t="inlineStr">
+      <c r="M42" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
+      <c r="A43" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>BENTHOTA DEVAGE</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> UDARA MADUSAKA</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <t>Sri Lanka</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>Butler</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
         <is>
           <t>PUQ, TBC</t>
         </is>
       </c>
-      <c r="J43" s="4" t="inlineStr">
+      <c r="J43" s="6" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="K43" s="4" t="inlineStr">
+      <c r="K43" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="L43" s="4" t="inlineStr">
+      <c r="L43" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M43" s="4" t="inlineStr">
+      <c r="M43" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="n">
+      <c r="A44" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>WILFEDO</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>MANAOG</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>Butcher</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I44" s="4" t="inlineStr">
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
         <is>
           <t>PUQ, Kran Keen</t>
         </is>
       </c>
-      <c r="J44" s="4" t="inlineStr">
+      <c r="J44" s="6" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="K44" s="4" t="inlineStr">
+      <c r="K44" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L44" s="4" t="inlineStr">
+      <c r="L44" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M44" s="4" t="inlineStr">
+      <c r="M44" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n">
+      <c r="A45" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>PHILIP</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>SOUTHIVEI RAO</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>f</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>Beautician</t>
         </is>
       </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I45" s="4" t="inlineStr">
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
         <is>
           <t>PUQ, Los Navegantes</t>
         </is>
       </c>
-      <c r="J45" s="4" t="inlineStr">
+      <c r="J45" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="K45" s="4" t="inlineStr">
+      <c r="K45" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L45" s="4" t="inlineStr">
+      <c r="L45" s="6" t="inlineStr">
         <is>
           <t>doble f</t>
         </is>
       </c>
-      <c r="M45" s="4" t="inlineStr">
+      <c r="M45" s="6" t="inlineStr">
         <is>
           <t>AF</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="n">
+      <c r="A46" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>DIAZ CASTILLO</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> MANUEL</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <t>Congo</t>
         </is>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>Sommelier</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I46" s="4" t="inlineStr">
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
         <is>
           <t>PUQ, TBC</t>
         </is>
       </c>
-      <c r="J46" s="4" t="inlineStr">
+      <c r="J46" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="K46" s="4" t="inlineStr">
+      <c r="K46" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L46" s="4" t="inlineStr">
+      <c r="L46" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M46" s="4" t="inlineStr">
+      <c r="M46" s="6" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="n">
+      <c r="A47" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>AJIMON</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> ANANTHAKRISHNAN</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="G47" s="6" t="inlineStr">
         <is>
           <t>Suite Attendant</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I47" s="4" t="inlineStr">
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
         <is>
           <t>PUQ, TBC</t>
         </is>
       </c>
-      <c r="J47" s="4" t="inlineStr">
+      <c r="J47" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="K47" s="4" t="inlineStr">
+      <c r="K47" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L47" s="4" t="inlineStr">
+      <c r="L47" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M47" s="4" t="inlineStr">
+      <c r="M47" s="6" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="n">
+      <c r="A48" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>BOGA</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> FREADY HOMI</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G48" s="4" t="inlineStr">
+      <c r="G48" s="6" t="inlineStr">
         <is>
           <t>Security Guard</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I48" s="4" t="inlineStr">
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
         <is>
           <t>PUQ, Patagonia BB</t>
         </is>
       </c>
-      <c r="J48" s="4" t="inlineStr">
+      <c r="J48" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="K48" s="4" t="inlineStr">
+      <c r="K48" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L48" s="4" t="inlineStr">
+      <c r="L48" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M48" s="4" t="inlineStr">
+      <c r="M48" s="6" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>FERNANDES</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> ROYSTON</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="G49" s="6" t="inlineStr">
         <is>
           <t>Butler</t>
         </is>
       </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I49" s="4" t="inlineStr">
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
         <is>
           <t>PUQ, Patagonia BB</t>
         </is>
       </c>
-      <c r="J49" s="4" t="inlineStr">
+      <c r="J49" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="K49" s="4" t="inlineStr">
+      <c r="K49" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L49" s="4" t="inlineStr">
+      <c r="L49" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M49" s="4" t="inlineStr">
+      <c r="M49" s="6" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="n">
+      <c r="A50" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>NORONHA</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> BONIFACIO JOAO</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G50" s="4" t="inlineStr">
+      <c r="G50" s="6" t="inlineStr">
         <is>
           <t>Suite Attendant</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I50" s="4" t="inlineStr">
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
         <is>
           <t>PUQ, Patagonia BB</t>
         </is>
       </c>
-      <c r="J50" s="4" t="inlineStr">
+      <c r="J50" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="K50" s="4" t="inlineStr">
+      <c r="K50" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L50" s="4" t="inlineStr">
+      <c r="L50" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M50" s="4" t="inlineStr">
+      <c r="M50" s="6" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n">
+      <c r="A51" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>ADNYANA</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> PUTU WIDYA</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <t>Indonesia</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr">
+      <c r="G51" s="6" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I51" s="4" t="inlineStr">
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
         <is>
           <t>PUQ, Patagonia BB</t>
         </is>
       </c>
-      <c r="J51" s="4" t="inlineStr">
+      <c r="J51" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="K51" s="4" t="inlineStr">
+      <c r="K51" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L51" s="4" t="inlineStr">
+      <c r="L51" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M51" s="4" t="inlineStr">
+      <c r="M51" s="6" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="n">
+      <c r="A52" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>IRPAN</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>ARDIANSYAH</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <t>Indonesia</t>
         </is>
       </c>
-      <c r="G52" s="4" t="inlineStr">
+      <c r="G52" s="6" t="inlineStr">
         <is>
           <t>Laundry Man</t>
         </is>
       </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I52" s="4" t="inlineStr">
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
         <is>
           <t>PUQ, Patagonia BB</t>
         </is>
       </c>
-      <c r="J52" s="4" t="inlineStr">
+      <c r="J52" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="K52" s="4" t="inlineStr">
+      <c r="K52" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L52" s="4" t="inlineStr">
+      <c r="L52" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M52" s="4" t="inlineStr">
+      <c r="M52" s="6" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="n">
+      <c r="A53" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>ABHISHEK VIJAY</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>JADHAV</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G53" s="4" t="inlineStr">
+      <c r="G53" s="6" t="inlineStr">
         <is>
           <t>Butler</t>
         </is>
       </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I53" s="4" t="inlineStr">
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
         <is>
           <t>PUQ, Patagonia BB</t>
         </is>
       </c>
-      <c r="J53" s="4" t="inlineStr">
+      <c r="J53" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="K53" s="4" t="inlineStr">
+      <c r="K53" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L53" s="4" t="inlineStr">
+      <c r="L53" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M53" s="4" t="inlineStr">
+      <c r="M53" s="6" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="n">
+      <c r="A54" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>ERIC JOHN OBISPO</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>PERALTA</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G54" s="4" t="inlineStr">
+      <c r="G54" s="6" t="inlineStr">
         <is>
           <t>Chef De Cuisine</t>
         </is>
       </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I54" s="4" t="inlineStr">
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
         <is>
           <t>PUQ, Patagonia BB</t>
         </is>
       </c>
-      <c r="J54" s="4" t="inlineStr">
+      <c r="J54" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="K54" s="4" t="inlineStr">
+      <c r="K54" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L54" s="4" t="inlineStr">
+      <c r="L54" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M54" s="4" t="inlineStr">
+      <c r="M54" s="6" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="n">
+      <c r="A55" s="6" t="n">
         <v>47</v>
       </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>RIZALINO JR</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>JOAQUIN</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G55" s="4" t="inlineStr">
+      <c r="G55" s="6" t="inlineStr">
         <is>
           <t>Able Seaman</t>
         </is>
       </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I55" s="4" t="inlineStr">
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
         <is>
           <t>PUQ, Kran Keen</t>
         </is>
       </c>
-      <c r="J55" s="4" t="inlineStr">
+      <c r="J55" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="K55" s="4" t="inlineStr">
+      <c r="K55" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L55" s="4" t="inlineStr">
+      <c r="L55" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M55" s="4" t="inlineStr">
+      <c r="M55" s="6" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="n">
+      <c r="A56" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>MARK JULIUS</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t>BAUTISTA</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G56" s="4" t="inlineStr">
+      <c r="G56" s="6" t="inlineStr">
         <is>
           <t>Provision Man</t>
         </is>
       </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I56" s="4" t="inlineStr">
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
         <is>
           <t>PUQ, Kran Keen</t>
         </is>
       </c>
-      <c r="J56" s="4" t="inlineStr">
+      <c r="J56" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="K56" s="4" t="inlineStr">
+      <c r="K56" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L56" s="4" t="inlineStr">
+      <c r="L56" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M56" s="4" t="inlineStr">
+      <c r="M56" s="6" t="inlineStr">
         <is>
           <t>AD</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="n">
+      <c r="A57" s="6" t="n">
         <v>49</v>
       </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>STEPHEN REY</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>PETRACORTA</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G57" s="4" t="inlineStr">
+      <c r="G57" s="6" t="inlineStr">
         <is>
           <t>Cheft de Partie</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I57" s="4" t="inlineStr">
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
         <is>
           <t>PUQ, Patagonia BB</t>
         </is>
       </c>
-      <c r="J57" s="4" t="inlineStr">
+      <c r="J57" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="K57" s="4" t="inlineStr">
+      <c r="K57" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L57" s="4" t="inlineStr">
+      <c r="L57" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M57" s="4" t="inlineStr">
+      <c r="M57" s="6" t="inlineStr">
         <is>
           <t>AD</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="n">
+      <c r="A58" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>MGCINUMUZI</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t>JAYAGURU</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <t>Zimbabwe</t>
         </is>
       </c>
-      <c r="G58" s="4" t="inlineStr">
+      <c r="G58" s="6" t="inlineStr">
         <is>
           <t>Sommelier</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I58" s="4" t="inlineStr">
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
         <is>
           <t>PUQ, Los Navegantes</t>
         </is>
       </c>
-      <c r="J58" s="4" t="inlineStr">
+      <c r="J58" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="K58" s="4" t="inlineStr">
+      <c r="K58" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L58" s="4" t="inlineStr">
+      <c r="L58" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M58" s="4" t="inlineStr">
+      <c r="M58" s="6" t="inlineStr">
         <is>
           <t>AE</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="n">
+      <c r="A59" s="6" t="n">
         <v>51</v>
       </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>FELIPE</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>MICHEELSEN ROSS</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <t>Chile</t>
         </is>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>Expedition Field Staff</t>
         </is>
       </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I59" s="4" t="inlineStr">
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
         <is>
           <t>PUQ, Los Navegantes</t>
         </is>
       </c>
-      <c r="J59" s="4" t="inlineStr">
+      <c r="J59" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="K59" s="4" t="inlineStr">
+      <c r="K59" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L59" s="4" t="inlineStr">
+      <c r="L59" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M59" s="4" t="inlineStr">
+      <c r="M59" s="6" t="inlineStr">
         <is>
           <t>AE</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="n">
+      <c r="A60" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>FULLER ALEGARBES</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t>LOMIBAO</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>Junior Nurse</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I60" s="4" t="inlineStr">
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
         <is>
           <t>PUQ, Los Navegantes</t>
         </is>
       </c>
-      <c r="J60" s="4" t="inlineStr">
+      <c r="J60" s="6" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="K60" s="4" t="inlineStr">
+      <c r="K60" s="6" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
-      <c r="L60" s="4" t="inlineStr">
+      <c r="L60" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M60" s="4" t="inlineStr">
+      <c r="M60" s="6" t="inlineStr">
         <is>
           <t>AG</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n">
+      <c r="A61" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> KANCHAN</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t>SHARMA</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="E61" s="6" t="inlineStr">
         <is>
           <t>f</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G61" s="6" t="inlineStr">
         <is>
           <t>Butler</t>
         </is>
       </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I61" s="4" t="inlineStr">
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
         <is>
           <t>PUQ, Art Noveau</t>
         </is>
       </c>
-      <c r="J61" s="4" t="inlineStr">
+      <c r="J61" s="6" t="inlineStr">
         <is>
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="K61" s="4" t="inlineStr">
+      <c r="K61" s="6" t="inlineStr">
         <is>
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="L61" s="4" t="inlineStr">
+      <c r="L61" s="6" t="inlineStr">
         <is>
           <t>doble f</t>
         </is>
       </c>
-      <c r="M61" s="4" t="inlineStr">
+      <c r="M61" s="6" t="inlineStr">
         <is>
           <t>AF</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="n">
+      <c r="A62" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> SUN</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D62" s="6" t="inlineStr">
         <is>
           <t>SHINE</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="E62" s="6" t="inlineStr">
         <is>
           <t>f</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <t>Myanmar</t>
         </is>
       </c>
-      <c r="G62" s="4" t="inlineStr">
+      <c r="G62" s="6" t="inlineStr">
         <is>
           <t>Waiter</t>
         </is>
       </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I62" s="4" t="inlineStr">
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
         <is>
           <t>PUQ, Art Noveau</t>
         </is>
       </c>
-      <c r="J62" s="4" t="inlineStr">
+      <c r="J62" s="6" t="inlineStr">
         <is>
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="K62" s="4" t="inlineStr">
+      <c r="K62" s="6" t="inlineStr">
         <is>
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="L62" s="4" t="inlineStr">
+      <c r="L62" s="6" t="inlineStr">
         <is>
           <t>doble f</t>
         </is>
       </c>
-      <c r="M62" s="4" t="inlineStr">
+      <c r="M62" s="6" t="inlineStr">
         <is>
           <t>AS</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="n">
+      <c r="A63" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> PHANI</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>ANUMUKONDA</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="G63" s="6" t="inlineStr">
         <is>
           <t>Butler</t>
         </is>
       </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I63" s="4" t="inlineStr">
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
         <is>
           <t>PUQ, Art Noveau</t>
         </is>
       </c>
-      <c r="J63" s="4" t="inlineStr">
+      <c r="J63" s="6" t="inlineStr">
         <is>
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="K63" s="4" t="inlineStr">
+      <c r="K63" s="6" t="inlineStr">
         <is>
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="L63" s="4" t="inlineStr">
+      <c r="L63" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M63" s="4" t="inlineStr">
+      <c r="M63" s="6" t="inlineStr">
         <is>
           <t>AG</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="n">
+      <c r="A64" s="6" t="n">
         <v>56</v>
       </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> KIRTI KUMAR</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D64" s="6" t="inlineStr">
         <is>
           <t>JENA</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G64" s="4" t="inlineStr">
+      <c r="G64" s="6" t="inlineStr">
         <is>
           <t>Service Assistant</t>
         </is>
       </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I64" s="4" t="inlineStr">
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
         <is>
           <t>PUQ, Art Noveau</t>
         </is>
       </c>
-      <c r="J64" s="4" t="inlineStr">
+      <c r="J64" s="6" t="inlineStr">
         <is>
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="K64" s="4" t="inlineStr">
+      <c r="K64" s="6" t="inlineStr">
         <is>
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="L64" s="4" t="inlineStr">
+      <c r="L64" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M64" s="4" t="inlineStr">
+      <c r="M64" s="6" t="inlineStr">
         <is>
           <t>AH</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="n">
+      <c r="A65" s="6" t="n">
         <v>57</v>
       </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> DEEPAK</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t>KESHTWAL</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G65" s="4" t="inlineStr">
+      <c r="G65" s="6" t="inlineStr">
         <is>
           <t>Butler</t>
         </is>
       </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I65" s="4" t="inlineStr">
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
         <is>
           <t>PUQ, Art Noveau</t>
         </is>
       </c>
-      <c r="J65" s="4" t="inlineStr">
+      <c r="J65" s="6" t="inlineStr">
         <is>
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="K65" s="4" t="inlineStr">
+      <c r="K65" s="6" t="inlineStr">
         <is>
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="L65" s="4" t="inlineStr">
+      <c r="L65" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M65" s="4" t="inlineStr">
+      <c r="M65" s="6" t="inlineStr">
         <is>
           <t>AH</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="n">
+      <c r="A66" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> SAGAR </t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D66" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">LNU </t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G66" s="4" t="inlineStr">
+      <c r="G66" s="6" t="inlineStr">
         <is>
           <t>Butler</t>
         </is>
       </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I66" s="4" t="inlineStr">
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
         <is>
           <t>PUQ, Art Noveau</t>
         </is>
       </c>
-      <c r="J66" s="4" t="inlineStr">
+      <c r="J66" s="6" t="inlineStr">
         <is>
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="K66" s="4" t="inlineStr">
+      <c r="K66" s="6" t="inlineStr">
         <is>
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="L66" s="4" t="inlineStr">
+      <c r="L66" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M66" s="4" t="inlineStr">
+      <c r="M66" s="6" t="inlineStr">
         <is>
           <t>AJ</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="n">
+      <c r="A67" s="6" t="n">
         <v>59</v>
       </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> RIZWAN</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t>SHAGUL HAMEED</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G67" s="4" t="inlineStr">
+      <c r="G67" s="6" t="inlineStr">
         <is>
           <t>Executive Sous Chef</t>
         </is>
       </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I67" s="4" t="inlineStr">
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
         <is>
           <t>PUQ, Diego de Almagro</t>
         </is>
       </c>
-      <c r="J67" s="4" t="inlineStr">
+      <c r="J67" s="6" t="inlineStr">
         <is>
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="K67" s="4" t="inlineStr">
+      <c r="K67" s="6" t="inlineStr">
         <is>
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="L67" s="4" t="inlineStr">
+      <c r="L67" s="6" t="inlineStr">
         <is>
           <t>single m</t>
         </is>
       </c>
-      <c r="M67" s="4" t="inlineStr">
+      <c r="M67" s="6" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="n">
+      <c r="A68" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> LAIJU</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D68" s="6" t="inlineStr">
         <is>
           <t>THOMAS</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G68" s="4" t="inlineStr">
+      <c r="G68" s="6" t="inlineStr">
         <is>
           <t>Chef De Partie</t>
         </is>
       </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I68" s="4" t="inlineStr">
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
         <is>
           <t>PUQ, Art Noveau</t>
         </is>
       </c>
-      <c r="J68" s="4" t="inlineStr">
+      <c r="J68" s="6" t="inlineStr">
         <is>
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="K68" s="4" t="inlineStr">
+      <c r="K68" s="6" t="inlineStr">
         <is>
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="L68" s="4" t="inlineStr">
+      <c r="L68" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M68" s="4" t="inlineStr">
+      <c r="M68" s="6" t="inlineStr">
         <is>
           <t>AJ</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="n">
+      <c r="A69" s="6" t="n">
         <v>61</v>
       </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> FNU</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr">
         <is>
           <t>TEGUH</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <t>Indonesia</t>
         </is>
       </c>
-      <c r="G69" s="4" t="inlineStr">
+      <c r="G69" s="6" t="inlineStr">
         <is>
           <t>Laundry Man</t>
         </is>
       </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I69" s="4" t="inlineStr">
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
         <is>
           <t>PUQ, Art Noveau</t>
         </is>
       </c>
-      <c r="J69" s="4" t="inlineStr">
+      <c r="J69" s="6" t="inlineStr">
         <is>
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="K69" s="4" t="inlineStr">
+      <c r="K69" s="6" t="inlineStr">
         <is>
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="L69" s="4" t="inlineStr">
+      <c r="L69" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M69" s="4" t="inlineStr">
+      <c r="M69" s="6" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="n">
+      <c r="A70" s="6" t="n">
         <v>62</v>
       </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> ALCIDES IVAN</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="D70" s="6" t="inlineStr">
         <is>
           <t>PONTE VARA</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <t>Peru</t>
         </is>
       </c>
-      <c r="G70" s="4" t="inlineStr">
+      <c r="G70" s="6" t="inlineStr">
         <is>
           <t>IT/Communications Officer</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I70" s="4" t="inlineStr">
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
         <is>
           <t>PUQ, Diego de Almagro</t>
         </is>
       </c>
-      <c r="J70" s="4" t="inlineStr">
+      <c r="J70" s="6" t="inlineStr">
         <is>
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="K70" s="4" t="inlineStr">
+      <c r="K70" s="6" t="inlineStr">
         <is>
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="L70" s="4" t="inlineStr">
+      <c r="L70" s="6" t="inlineStr">
         <is>
           <t>single m</t>
         </is>
       </c>
-      <c r="M70" s="4" t="inlineStr">
+      <c r="M70" s="6" t="inlineStr">
         <is>
           <t>AK</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="n">
+      <c r="A71" s="6" t="n">
         <v>63</v>
       </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> JONATHAN</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr">
         <is>
           <t>BALANCIO</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G71" s="4" t="inlineStr">
+      <c r="G71" s="6" t="inlineStr">
         <is>
           <t>Able Seaman</t>
         </is>
       </c>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I71" s="4" t="inlineStr">
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
         <is>
           <t>PUQ, Art Noveau</t>
         </is>
       </c>
-      <c r="J71" s="4" t="inlineStr">
+      <c r="J71" s="6" t="inlineStr">
         <is>
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="K71" s="4" t="inlineStr">
+      <c r="K71" s="6" t="inlineStr">
         <is>
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="L71" s="4" t="inlineStr">
+      <c r="L71" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M71" s="4" t="inlineStr">
+      <c r="M71" s="6" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="n">
+      <c r="A72" s="6" t="n">
         <v>64</v>
       </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> ERMIE</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="D72" s="6" t="inlineStr">
         <is>
           <t>CARINO</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G72" s="4" t="inlineStr">
+      <c r="G72" s="6" t="inlineStr">
         <is>
           <t>Chef De Partie</t>
         </is>
       </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I72" s="4" t="inlineStr">
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
         <is>
           <t>PUQ, Art Noveau</t>
         </is>
       </c>
-      <c r="J72" s="4" t="inlineStr">
+      <c r="J72" s="6" t="inlineStr">
         <is>
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="K72" s="4" t="inlineStr">
+      <c r="K72" s="6" t="inlineStr">
         <is>
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="L72" s="4" t="inlineStr">
+      <c r="L72" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M72" s="4" t="inlineStr">
+      <c r="M72" s="6" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="n">
+      <c r="A73" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> WILLIAM</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
+      <c r="D73" s="6" t="inlineStr">
         <is>
           <t>DOLLENTAS</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G73" s="4" t="inlineStr">
+      <c r="G73" s="6" t="inlineStr">
         <is>
           <t>Chef De Cuisine</t>
         </is>
       </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I73" s="4" t="inlineStr">
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
         <is>
           <t>PUQ, Art Noveau</t>
         </is>
       </c>
-      <c r="J73" s="4" t="inlineStr">
+      <c r="J73" s="6" t="inlineStr">
         <is>
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="K73" s="4" t="inlineStr">
+      <c r="K73" s="6" t="inlineStr">
         <is>
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="L73" s="4" t="inlineStr">
+      <c r="L73" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M73" s="4" t="inlineStr">
+      <c r="M73" s="6" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="n">
+      <c r="A74" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> JERUH FULAY</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
+      <c r="D74" s="6" t="inlineStr">
         <is>
           <t>FLORIDA</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G74" s="4" t="inlineStr">
+      <c r="G74" s="6" t="inlineStr">
         <is>
           <t>Carpenter</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I74" s="4" t="inlineStr">
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
         <is>
           <t>PUQ, Art Noveau</t>
         </is>
       </c>
-      <c r="J74" s="4" t="inlineStr">
+      <c r="J74" s="6" t="inlineStr">
         <is>
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="K74" s="4" t="inlineStr">
+      <c r="K74" s="6" t="inlineStr">
         <is>
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="L74" s="4" t="inlineStr">
+      <c r="L74" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M74" s="4" t="inlineStr">
+      <c r="M74" s="6" t="inlineStr">
         <is>
           <t>AN</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="n">
+      <c r="A75" s="6" t="n">
         <v>67</v>
       </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> EDUARD FLORES</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>MARIKIT</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G75" s="4" t="inlineStr">
+      <c r="G75" s="6" t="inlineStr">
         <is>
           <t>Able Seaman</t>
         </is>
       </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I75" s="4" t="inlineStr">
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
         <is>
           <t>PUQ, Art Noveau</t>
         </is>
       </c>
-      <c r="J75" s="4" t="inlineStr">
+      <c r="J75" s="6" t="inlineStr">
         <is>
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="K75" s="4" t="inlineStr">
+      <c r="K75" s="6" t="inlineStr">
         <is>
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="L75" s="4" t="inlineStr">
+      <c r="L75" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M75" s="4" t="inlineStr">
+      <c r="M75" s="6" t="inlineStr">
         <is>
           <t>AN</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="n">
+      <c r="A76" s="6" t="n">
         <v>68</v>
       </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> NORBERTO</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="D76" s="6" t="inlineStr">
         <is>
           <t>OXENO</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G76" s="4" t="inlineStr">
+      <c r="G76" s="6" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I76" s="4" t="inlineStr">
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
         <is>
           <t>PUQ, Diego de Almagro</t>
         </is>
       </c>
-      <c r="J76" s="4" t="inlineStr">
+      <c r="J76" s="6" t="inlineStr">
         <is>
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="K76" s="4" t="inlineStr">
+      <c r="K76" s="6" t="inlineStr">
         <is>
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="L76" s="4" t="inlineStr">
+      <c r="L76" s="6" t="inlineStr">
         <is>
           <t>single m</t>
         </is>
       </c>
-      <c r="M76" s="4" t="inlineStr">
+      <c r="M76" s="6" t="inlineStr">
         <is>
           <t>AO</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="n">
+      <c r="A77" s="6" t="n">
         <v>69</v>
       </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> GEM LASKER ARCELO</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
+      <c r="D77" s="6" t="inlineStr">
         <is>
           <t>PURIO</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G77" s="4" t="inlineStr">
+      <c r="G77" s="6" t="inlineStr">
         <is>
           <t>Provision Man</t>
         </is>
       </c>
-      <c r="H77" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I77" s="4" t="inlineStr">
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
         <is>
           <t>PUQ, Art Noveau</t>
         </is>
       </c>
-      <c r="J77" s="4" t="inlineStr">
+      <c r="J77" s="6" t="inlineStr">
         <is>
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="K77" s="4" t="inlineStr">
+      <c r="K77" s="6" t="inlineStr">
         <is>
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="L77" s="4" t="inlineStr">
+      <c r="L77" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M77" s="4" t="inlineStr">
+      <c r="M77" s="6" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="n">
+      <c r="A78" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> NANDLAL</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="D78" s="6" t="inlineStr">
         <is>
           <t>RAJBHAR</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G78" s="4" t="inlineStr">
+      <c r="G78" s="6" t="inlineStr">
         <is>
           <t>Galley Utility</t>
         </is>
       </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I78" s="4" t="inlineStr">
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
         <is>
           <t>PUQ, Art Noveau</t>
         </is>
       </c>
-      <c r="J78" s="4" t="inlineStr">
+      <c r="J78" s="6" t="inlineStr">
         <is>
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="K78" s="4" t="inlineStr">
+      <c r="K78" s="6" t="inlineStr">
         <is>
           <t>2024-11-20</t>
         </is>
       </c>
-      <c r="L78" s="4" t="inlineStr">
+      <c r="L78" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M78" s="4" t="inlineStr">
+      <c r="M78" s="6" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="n">
+      <c r="A79" s="6" t="n">
         <v>71</v>
       </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> ERIK MARIONNE MANUIT</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="D79" s="6" t="inlineStr">
         <is>
           <t>JATULAN</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G79" s="4" t="inlineStr">
+      <c r="G79" s="6" t="inlineStr">
         <is>
           <t>Galley Utility</t>
         </is>
       </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I79" s="4" t="inlineStr">
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
         <is>
           <t>PUQ, Art Noveau</t>
         </is>
       </c>
-      <c r="J79" s="4" t="inlineStr">
+      <c r="J79" s="6" t="inlineStr">
         <is>
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="K79" s="4" t="inlineStr">
+      <c r="K79" s="6" t="inlineStr">
         <is>
           <t>2024-11-20</t>
         </is>
       </c>
-      <c r="L79" s="4" t="inlineStr">
+      <c r="L79" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M79" s="4" t="inlineStr">
+      <c r="M79" s="6" t="inlineStr">
         <is>
           <t>AQ</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="n">
+      <c r="A80" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> JUSTIN HANNS ORTIZO</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D80" s="6" t="inlineStr">
         <is>
           <t>LANIOG</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G80" s="4" t="inlineStr">
+      <c r="G80" s="6" t="inlineStr">
         <is>
           <t>Desktop Publisher</t>
         </is>
       </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I80" s="4" t="inlineStr">
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
         <is>
           <t>PUQ, Art Noveau</t>
         </is>
       </c>
-      <c r="J80" s="4" t="inlineStr">
+      <c r="J80" s="6" t="inlineStr">
         <is>
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="K80" s="4" t="inlineStr">
+      <c r="K80" s="6" t="inlineStr">
         <is>
           <t>2024-11-20</t>
         </is>
       </c>
-      <c r="L80" s="4" t="inlineStr">
+      <c r="L80" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M80" s="4" t="inlineStr">
+      <c r="M80" s="6" t="inlineStr">
         <is>
           <t>AQ</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="n">
+      <c r="A81" s="6" t="n">
         <v>73</v>
       </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>Silversea</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>Silversea</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> RODNEY</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>SENO</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="G81" s="4" t="inlineStr">
+      <c r="G81" s="6" t="inlineStr">
         <is>
           <t>Suite Attendant</t>
         </is>
       </c>
-      <c r="H81" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I81" s="4" t="inlineStr">
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
         <is>
           <t>PUQ, Art Noveau</t>
         </is>
       </c>
-      <c r="J81" s="4" t="inlineStr">
+      <c r="J81" s="6" t="inlineStr">
         <is>
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="K81" s="4" t="inlineStr">
+      <c r="K81" s="6" t="inlineStr">
         <is>
           <t>2024-11-20</t>
         </is>
       </c>
-      <c r="L81" s="4" t="inlineStr">
+      <c r="L81" s="6" t="inlineStr">
         <is>
           <t>doble m</t>
         </is>
       </c>
-      <c r="M81" s="4" t="inlineStr">
+      <c r="M81" s="6" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
